--- a/data/processed/daily_rosters_excels/roster_2026-01-18.xlsx
+++ b/data/processed/daily_rosters_excels/roster_2026-01-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4120,29 +4120,29 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WARi</t>
+          <t>EFm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Team wari</t>
+          <t>Edward Fm</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3146557</v>
+        <v>5104157</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1629111</t>
+          <t>1641705</t>
         </is>
       </c>
     </row>
@@ -4171,26 +4171,26 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5104157</v>
+        <v>4433134</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1641705</t>
+          <t>1630567</t>
         </is>
       </c>
     </row>
@@ -4209,16 +4209,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4433134</v>
+        <v>4684740</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1630567</t>
+          <t>1641708</t>
         </is>
       </c>
     </row>
@@ -4247,26 +4247,26 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4684740</v>
+        <v>4869342</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1641708</t>
+          <t>1630700</t>
         </is>
       </c>
     </row>
@@ -4285,26 +4285,26 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4869342</v>
+        <v>1966</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1630700</t>
+          <t>2544</t>
         </is>
       </c>
     </row>
@@ -4323,26 +4323,26 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1966</v>
+        <v>4437244</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>1630224</t>
         </is>
       </c>
     </row>
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4437244</v>
+        <v>4683021</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1630224</t>
+          <t>1630166</t>
         </is>
       </c>
     </row>
@@ -4399,16 +4399,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4683021</v>
+        <v>4251</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1630166</t>
+          <t>202331</t>
         </is>
       </c>
     </row>
@@ -4437,26 +4437,26 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4251</v>
+        <v>3064290</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>202331</t>
+          <t>203932</t>
         </is>
       </c>
     </row>
@@ -4475,26 +4475,26 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3064290</v>
+        <v>4591725</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>203932</t>
+          <t>1631157</t>
         </is>
       </c>
     </row>
@@ -4513,26 +4513,26 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4591725</v>
+        <v>4397189</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Jalen Smith</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1631157</t>
+          <t>1630188</t>
         </is>
       </c>
     </row>
@@ -4551,26 +4551,26 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4397189</v>
+        <v>4277847</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jalen Smith</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1630188</t>
+          <t>1628976</t>
         </is>
       </c>
     </row>
@@ -4589,26 +4589,26 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4277847</v>
+        <v>5093267</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1628976</t>
+          <t>1642867</t>
         </is>
       </c>
     </row>
@@ -4627,64 +4627,64 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5093267</v>
+        <v>4397040</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1642867</t>
+          <t>1630314</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EFm</t>
+          <t>PPH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Edward Fm</t>
+          <t>Puerto Principe</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4592691</v>
+        <v>6583</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Anthony Davis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1631222</t>
+          <t>203076</t>
         </is>
       </c>
     </row>
@@ -4703,26 +4703,26 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6583</v>
+        <v>4431678</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Anthony Davis</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>203076</t>
+          <t>1630178</t>
         </is>
       </c>
     </row>
@@ -4741,26 +4741,26 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4431678</v>
+        <v>4871144</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1630178</t>
+          <t>1630578</t>
         </is>
       </c>
     </row>
@@ -4779,26 +4779,26 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4871144</v>
+        <v>4066320</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1630578</t>
+          <t>1630217</t>
         </is>
       </c>
     </row>
@@ -4817,26 +4817,26 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4066320</v>
+        <v>3147657</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1630217</t>
+          <t>1628969</t>
         </is>
       </c>
     </row>
@@ -4855,26 +4855,26 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3147657</v>
+        <v>4395724</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1628969</t>
+          <t>1630193</t>
         </is>
       </c>
     </row>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4395724</v>
+        <v>4433627</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Keyonte George</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1630193</t>
+          <t>1641718</t>
         </is>
       </c>
     </row>
@@ -4931,26 +4931,26 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4433627</v>
+        <v>4683634</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Keyonte George</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1641718</t>
+          <t>1631097</t>
         </is>
       </c>
     </row>
@@ -4969,26 +4969,26 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4683634</v>
+        <v>4432639</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1631097</t>
+          <t>1631095</t>
         </is>
       </c>
     </row>
@@ -5007,26 +5007,26 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4432639</v>
+        <v>4278039</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1631095</t>
+          <t>1629638</t>
         </is>
       </c>
     </row>
@@ -5045,26 +5045,26 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4278039</v>
+        <v>4278053</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1629638</t>
+          <t>1630558</t>
         </is>
       </c>
     </row>
@@ -5083,26 +5083,26 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4278053</v>
+        <v>4431736</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1630558</t>
+          <t>1641739</t>
         </is>
       </c>
     </row>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4431736</v>
+        <v>4576087</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1641739</t>
+          <t>1631212</t>
         </is>
       </c>
     </row>
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4576087</v>
+        <v>4903027</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5178,45 +5178,45 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1631212</t>
+          <t>1642907</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PPH</t>
+          <t>MMT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Puerto Principe</t>
+          <t>House of Mamba</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4903027</v>
+        <v>3975</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1642907</t>
+          <t>201939</t>
         </is>
       </c>
     </row>
@@ -5235,26 +5235,26 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3975</v>
+        <v>4433255</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>201939</t>
+          <t>1631096</t>
         </is>
       </c>
     </row>
@@ -5273,16 +5273,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4433255</v>
+        <v>4066261</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1631096</t>
+          <t>1628389</t>
         </is>
       </c>
     </row>
@@ -5311,26 +5311,26 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4066261</v>
+        <v>4593803</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1628389</t>
+          <t>1631114</t>
         </is>
       </c>
     </row>
@@ -5349,26 +5349,26 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4593803</v>
+        <v>4277956</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1631114</t>
+          <t>1629673</t>
         </is>
       </c>
     </row>
@@ -5387,26 +5387,26 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4277956</v>
+        <v>6589</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1629673</t>
+          <t>203110</t>
         </is>
       </c>
     </row>
@@ -5425,26 +5425,26 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6589</v>
+        <v>3468</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Russell Westbrook</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>203110</t>
+          <t>201566</t>
         </is>
       </c>
     </row>
@@ -5463,16 +5463,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3468</v>
+        <v>3995</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Russell Westbrook</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>201566</t>
+          <t>201950</t>
         </is>
       </c>
     </row>
@@ -5501,26 +5501,26 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3995</v>
+        <v>4065732</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>De'Andre Hunter</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>201950</t>
+          <t>1629631</t>
         </is>
       </c>
     </row>
@@ -5539,26 +5539,26 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4065732</v>
+        <v>3934673</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>De'Andre Hunter</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1629631</t>
+          <t>1628978</t>
         </is>
       </c>
     </row>
@@ -5577,26 +5577,26 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3934673</v>
+        <v>3908845</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1628978</t>
+          <t>1628381</t>
         </is>
       </c>
     </row>
@@ -5615,26 +5615,26 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3908845</v>
+        <v>4431767</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1628381</t>
+          <t>1631128</t>
         </is>
       </c>
     </row>
@@ -5653,26 +5653,26 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4431767</v>
+        <v>4593125</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1631128</t>
+          <t>1630583</t>
         </is>
       </c>
     </row>
@@ -5691,62 +5691,24 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4593125</v>
+        <v>5174563</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
-        <is>
-          <t>1630583</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>21</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>MMT</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>House of Mamba</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>5174563</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Kyshawn George</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
         <is>
           <t>1642273</t>
         </is>
